--- a/docs/collections/kanshi/metadata/data.xlsx
+++ b/docs/collections/kanshi/metadata/data.xlsx
@@ -1596,7 +1596,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>形態: [51] leaves of plates</t>
+          <t>形態: [51] leaves of plates|総合図書館・保存書庫に所蔵あり(請求記号 T350:624)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>表紙タイトル: 東京帝國大學附屬圖書館復興記念寫眞帖|その他のタイトル: 東京帝国大学附属図書館復興記念写真帖</t>
+          <t>表紙タイトル: 東京帝國大學附屬圖書館復興記念寫眞帖|その他のタイトル: 東京帝国大学附属図書館復興記念写真帖|総合図書館・保存書庫に所蔵あり(請求記号 A15:2166)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>形態: 42 leaves ; 33 × 43 cm.|その他のタイトル: 東大圖書館</t>
+          <t>形態: 42 leaves ; 33 × 43 cm.|その他のタイトル: 東大圖書館|総合図書館・保存書庫に所蔵あり(請求記号 BA:10)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">

--- a/docs/collections/kanshi/metadata/data.xlsx
+++ b/docs/collections/kanshi/metadata/data.xlsx
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>旧図書館外観 [1]</t>
+          <t>旧図書館外観(玄関) [1]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>旧図書館外観 [2]</t>
+          <t>旧図書館外観(玄関) [2]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/docs/collections/kanshi/metadata/data.xlsx
+++ b/docs/collections/kanshi/metadata/data.xlsx
@@ -1693,12 +1693,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ヘラルド社</t>
+          <t>東京帝國大學附屬圖書館</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1930-11</t>
+          <t>1930-03</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>表紙タイトル: 東京帝國大學附屬圖書館復興記念寫眞帖|その他のタイトル: 東京帝国大学附属図書館復興記念写真帖|総合図書館・保存書庫に所蔵あり(請求記号 A15:2166)</t>
+          <t>表紙タイトル: 東京帝國大學附屬圖書館復興記念寫眞帖|その他のタイトル: 東京帝国大学附属図書館復興記念写真帖|総合図書館・保存書庫に所蔵あり(請求記号 A15:322, K40:765)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
